--- a/data/採購網_決標彙整.xlsx
+++ b/data/採購網_決標彙整.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,35 +627,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A.15.3.4</t>
+          <t>43862061</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>交通部公路局東區養護工程分局</t>
+          <t>長庚醫療財團法人林口長庚紀念醫院</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>台2線桶盤堀橋改建工程委託測量、地質探查、綜合規劃及設計服務工作</t>
+          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16444921</v>
+        <v>2390000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjM4OTY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -712,35 +712,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>A.15.3.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>交通部公路局東區養護工程分局</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115年地政業務地理資訊應用系統增修維護案</t>
+          <t>台2線桶盤堀橋改建工程委託測量、地質探查、綜合規劃及設計服務工作</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2200000</v>
+        <v>16444921</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjM4OTY</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -795,25 +795,37 @@
           <t>20260617</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.13.52.10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>台灣自來水股份有限公司第十區管理處</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>臺東縣</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>「5-L醱酵槽數位模型優化及數位影子建置」委託研究計畫案</t>
+          <t>本處113年度新裝及修漏圖資實測定位作業</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1838580</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20251002&amp;fn=PPW-1-70080650.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260617&amp;fn=BDM-1-71207686.xml</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -829,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -853,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -870,35 +882,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.95.25</t>
+          <t>3.79.14.14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臺南市政府水利局</t>
+          <t>臺北市立聯合醫院</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115年臺南市污水下水道地理資訊系統維護及擴充委託資訊服務</t>
+          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5000000</v>
+        <v>686000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTc5NjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -908,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -926,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -955,35 +967,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43862061</t>
+          <t>3.95.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>長庚醫療財團法人林口長庚紀念醫院</t>
+          <t>臺南市政府水利局</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
+          <t>115年臺南市污水下水道地理資訊系統維護及擴充委託資訊服務</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2390000</v>
+        <v>5000000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTc5NjY</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -993,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1011,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1038,37 +1050,25 @@
           <t>20260617</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.13.52.10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>台灣自來水股份有限公司第十區管理處</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>臺東縣</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本處113年度新裝及修漏圖資實測定位作業</t>
+          <t>「5-L醱酵槽數位模型優化及數位影子建置」委託研究計畫案</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1838580</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260617&amp;fn=BDM-1-71207686.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20251002&amp;fn=PPW-1-70080650.xml</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1120,40 +1120,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10.94.24XX</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>樹人醫護管理專科學校</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>護理科嬰兒安妮模型等</t>
+          <t>115年地政業務地理資訊應用系統增修維護案</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>278000</v>
+        <v>2200000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTQ2NjA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>94569104</t>
+          <t>3.10.94.24XX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>國家運動科學中心</t>
+          <t>樹人醫護管理專科學校</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1230,15 +1230,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115年度鞋內動態壓力分佈測量系統案</t>
+          <t>護理科嬰兒安妮模型等</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1680000</v>
+        <v>278000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260616&amp;fn=BDM-1-71205201.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTQ2NjA</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1295,35 +1295,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.80.16.24</t>
+          <t>94569104</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>桃園市楊梅地政事務所</t>
+          <t>國家運動科學中心</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>115年度圖根點清理與新補建測量作業</t>
+          <t>115年度鞋內動態壓力分佈測量系統案</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>720000</v>
+        <v>1680000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjk4MTI</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260616&amp;fn=BDM-1-71205201.xml</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1375,40 +1375,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.87.5.1</t>
+          <t>3.80.16.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>臺中市立大甲高級中等學校</t>
+          <t>桃園市楊梅地政事務所</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>115年國教署補助公民營機構研習-熱炒食堂-食物模型製作勞務採購案</t>
+          <t>115年度圖根點清理與新補建測量作業</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>225000</v>
+        <v>720000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzEyMDU2MzI=</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjk4MTI</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1460,28 +1460,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260612</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3.87.5.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>臺中市立大甲高級中等學校</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>臺中市</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>115年臺中港鄰近海域地形測量</t>
+          <t>115年國教署補助公民營機構研習-熱炒食堂-食物模型製作勞務採購案</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260119&amp;fn=PPW-1-70090864.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzEyMDU2MzI=</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1491,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1503,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1521,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1536,37 +1548,25 @@
           <t>20260612</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>06479492</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>長榮大學</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>臺南市</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>圖資處電腦教室硬體廣播系統採購案</t>
+          <t>115年臺中港鄰近海域地形測量</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1750000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTQwODY</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260119&amp;fn=PPW-1-70090864.xml</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1576,19 +1576,19 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1612,50 +1612,50 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.1.100.1</t>
+          <t>06479492</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>內政部國土測繪中心</t>
+          <t>長榮大學</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>115年及116年國土測繪圖資服務雲擴充及維護採購案</t>
+          <t>圖資處電腦教室硬體廣播系統採購案</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19500000</v>
+        <v>1750000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDgzNDY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTQwODY</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1697,50 +1697,62 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260610</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.1.100.1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>內政部國土測繪中心</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>臺中市</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>臺北市政府地政局所屬所隊115年度測量儀器聯合財物採購案</t>
+          <t>115年及116年國土測繪圖資服務雲擴充及維護採購案</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>19500000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260327&amp;fn=PPW-1-70097357.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDgzNDY</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1770,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1781,42 +1793,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A.19.9</t>
+          <t>3.9.31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>農業部農業試驗所</t>
+          <t>國立中正大學</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>農業環境空間資訊整合及資通訊工具應用推廣教育訓練</t>
+          <t>115年圖資大樓廁所整修工程</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4100000</v>
+        <v>4610954</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTEwMDU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1825,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1864,37 +1876,25 @@
           <t>20260610</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A.9.6J</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>國立屏東大學</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>屏東縣</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
+          <t>臺北市政府地政局所屬所隊115年度測量儀器聯合財物採購案</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>7152000</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260327&amp;fn=PPW-1-70097357.xml</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.9.31</t>
+          <t>A.9.6J</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>國立中正大學</t>
+          <t>國立屏東大學</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1971,15 +1971,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>115年圖資大樓廁所整修工程</t>
+          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4610954</v>
+        <v>7152000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2031,50 +2031,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A.17.2.2</t>
+          <t>A.19.9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>農業部農業試驗所</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>115年微電腦測量儀（水量測試儀）及專用電腦1批採購案</t>
+          <t>農業環境空間資訊整合及資通訊工具應用推廣教育訓練</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>676000</v>
+        <v>4100000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjY1ODY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTEwMDU</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2121,17 +2121,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>A.17.2.2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2141,15 +2141,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>115年度數值地形模型系統維運與加值應用推廣案</t>
+          <t>115年微電腦測量儀（水量測試儀）及專用電腦1批採購案</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1300000</v>
+        <v>676000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk1Nzc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjY1ODY</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2206,35 +2206,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A.1.3.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>內政部國家公園署台江國家公園管理處</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>115年度基礎地理圖資查詢及應用系統案</t>
+          <t>115年度數值地形模型系統維運與加值應用推廣案</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2200000</v>
+        <v>1300000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUyMzE</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk1Nzc</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2250,13 +2250,13 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2274,52 +2274,52 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.1.100.1</t>
+          <t>A.1.3.8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>內政部國土測繪中心</t>
+          <t>內政部國家公園署台江國家公園管理處</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>115年度三維建物模型更新及精進採購案</t>
+          <t>115年度基礎地理圖資查詢及應用系統案</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>18000000</v>
+        <v>2200000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUyMzE</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2376,35 +2376,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.76.44</t>
+          <t>3.10.90.19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>南臺學校財團法人南臺科技大學</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
+          <t>平台式切削動力計測量系統乙套</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7125000</v>
+        <v>2353063</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQxODM</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2414,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2459,25 +2459,37 @@
           <t>20260608</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>內政部</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>115-116年東部近岸地形監測</t>
+          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>31000000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260223&amp;fn=PPW-1-70093777.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2493,13 +2505,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2534,17 +2546,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.10.99.62</t>
+          <t>3.76.44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>景文科技大學</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2554,15 +2566,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>115圖資處獎補助中文圖書採購案</t>
+          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>300000</v>
+        <v>7125000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2619,35 +2631,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3.10.90.19</t>
+          <t>3.10.99.62</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>南臺學校財團法人南臺科技大學</t>
+          <t>景文科技大學</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>平台式切削動力計測量系統乙套</t>
+          <t>115圖資處獎補助中文圖書採購案</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2353063</v>
+        <v>300000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQxODM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2657,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2702,37 +2714,25 @@
           <t>20260608</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>內政部</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>臺北市</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
+          <t>115-116年東部近岸地形監測</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>31000000</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260223&amp;fn=PPW-1-70093777.xml</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2748,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2784,40 +2784,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A.15.3.5</t>
+          <t>3.1.100.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>交通部公路局雲嘉南區養護工程分局</t>
+          <t>內政部國土測繪中心</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>115~117年工程委託測量設計服務工作(開口契約)</t>
+          <t>115年度三維建物模型更新及精進採購案</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>10726504</v>
+        <v>18000000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzY2MDU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwMTM</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2874,17 +2874,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3.9.26.3</t>
+          <t>A.15.3.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>國立成功大學醫學院附設醫院</t>
+          <t>交通部公路局雲嘉南區養護工程分局</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2894,15 +2894,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>掃頻式人工水晶體光學測量儀1組</t>
+          <t>115~117年工程委託測量設計服務工作(開口契約)</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3000000</v>
+        <v>10726504</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzU1MjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzY2MDU</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2954,40 +2954,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3.87.33.40</t>
+          <t>3.9.26.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>臺中市立美術館</t>
+          <t>國立成功大學醫學院附設醫院</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>「115年王水河設計地圖推廣採購案」</t>
+          <t>掃頻式人工水晶體光學測量儀1組</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>750000</v>
+        <v>3000000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQyNTI</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzU1MjY</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3044,17 +3044,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A.19.6</t>
+          <t>3.87.33.40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺中市立美術館</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3064,15 +3064,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>115年GNSS 全球衛星定位測量儀器採購案</t>
+          <t>「115年王水河設計地圖推廣採購案」</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2000000</v>
+        <v>750000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjI1NDY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQyNTI</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3129,35 +3129,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.76.42</t>
+          <t>A.19.6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>115年度河川疏濬規劃之地形測量及疏濬期間測量作業(第1次後續擴充)</t>
+          <t>115年GNSS 全球衛星定位測量儀器採購案</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2088520</v>
+        <v>2000000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260604&amp;fn=BDM-1-71196667.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjI1NDY</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3214,35 +3214,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A.19.6</t>
+          <t>3.76.42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>115-116年度無人飛行載具正射影像產製暨渠道圖資調查研析更新計畫</t>
+          <t>115年度河川疏濬規劃之地形測量及疏濬期間測量作業(第1次後續擴充)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5280000</v>
+        <v>2088520</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTczMzE</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260604&amp;fn=BDM-1-71196667.xml</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3252,19 +3252,19 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3299,35 +3299,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A.1.3.9</t>
+          <t>A.19.6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>內政部國家公園署國家自然公園管理處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>115年度國家自然公園土地管理地理資訊系統維運案</t>
+          <t>115-116年度無人飛行載具正射影像產製暨渠道圖資調查研析更新計畫</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>456000</v>
+        <v>5280000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDI0MTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTczMzE</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3384,35 +3384,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A.9.6M.1</t>
+          <t>A.1.3.9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>國立陽明交通大學附設醫院</t>
+          <t>內政部國家公園署國家自然公園管理處</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>眼科生物測量近視控制系統軟體1套</t>
+          <t>115年度國家自然公園土地管理地理資訊系統維運案</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>450000</v>
+        <v>456000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTc2MzA=</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDI0MTM</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3464,40 +3464,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3.80.11</t>
+          <t>A.9.6M.1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>國立陽明交通大學附設醫院</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>115年度桃園市工廠地理資訊暨稽查管理系統維護計畫</t>
+          <t>眼科生物測量近視控制系統軟體1套</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1420000</v>
+        <v>450000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTUxOTk</t>
+          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTc2MzA=</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3549,40 +3549,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3.97.13.3</t>
+          <t>3.80.11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>高雄市政府警察局交通警察大隊</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>115年度「交通事故處理淨零轉型專案-建置易肇事路⼝街廓圖資」勞務採購限制性招標案</t>
+          <t>115年度桃園市工廠地理資訊暨稽查管理系統維護計畫</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>750000</v>
+        <v>1420000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTU0NjE=</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTUxOTk</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3639,35 +3639,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A.7.31.1</t>
+          <t>3.97.13.3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>臺灣銀行股份有限公司</t>
+          <t>高雄市政府警察局交通警察大隊</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
+          <t>115年度「交通事故處理淨零轉型專案-建置易肇事路⼝街廓圖資」勞務採購限制性招標案</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1995000</v>
+        <v>750000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTU0NjE=</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3719,17 +3719,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3.79.67.1</t>
+          <t>A.7.31.1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>臺北市市場處</t>
+          <t>臺灣銀行股份有限公司</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3744,15 +3744,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
+          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>209000</v>
+        <v>1995000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>99334269</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>法務部</t>
+          <t>台灣休閒農業學會</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3829,15 +3829,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
+          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3.97.5.4</t>
+          <t>A.13.6.3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>高雄市立林園高級中學</t>
+          <t>經濟部水利署南區水資源分署</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3914,15 +3914,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>圖資大樓後續擴充室內裝修工程</t>
+          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>13973553</v>
+        <v>1921585</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3932,13 +3932,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A.13.6.3</t>
+          <t>3.97.5.4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>經濟部水利署南區水資源分署</t>
+          <t>高雄市立林園高級中學</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3999,15 +3999,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
+          <t>圖資大樓後續擴充室內裝修工程</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1921585</v>
+        <v>13973553</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4017,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>99334269</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>台灣休閒農業學會</t>
+          <t>法務部</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4084,15 +4084,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
+          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4144,17 +4144,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.79.11</t>
+          <t>3.79.67.1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>臺北市市場處</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4169,15 +4169,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>115年度管線圖資更新品質案件抽查及抽測作業</t>
+          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7745000</v>
+        <v>209000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODYwNzM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>中央研究院</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4339,25 +4339,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
+          <t>光鑷與直接式力測量系統</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3080000</v>
+        <v>6900000</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191365.xml</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4404,35 +4404,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.87.32</t>
+          <t>3.79.11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>臺中市政府消防局</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>成人全身QCPR心肺復甦訓練模型</t>
+          <t>115年度管線圖資更新品質案件抽查及抽測作業</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1800000</v>
+        <v>7745000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODYwNzM</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -4489,35 +4489,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.95.25</t>
+          <t>3.13.20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>臺南市政府水利局</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>114年臺南市永華行政區雨水箱涵調查及圖資補正作業(開口合約)(第1次後續擴充)</t>
+          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>8000000</v>
+        <v>5100000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191343.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4574,35 +4574,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A.15.3.2</t>
+          <t>A.15.6.10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>交通部民用航空局馬祖航空站</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>連江縣</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>離島</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
+          <t>南竿機場新建模鑄型高壓變壓器故障委託鑑定案</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3960601</v>
+        <v>1228000</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzMTM</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>中央研究院</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4679,25 +4679,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>光鑷與直接式力測量系統</t>
+          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>6900000</v>
+        <v>3080000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191365.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4744,35 +4744,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A.15.6.10</t>
+          <t>A.15.3.2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>交通部民用航空局馬祖航空站</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>連江縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>離島</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>南竿機場新建模鑄型高壓變壓器故障委託鑑定案</t>
+          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1228000</v>
+        <v>3960601</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -4815,49 +4815,49 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3.92.1.27</t>
+          <t>3.95.25</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>國立北港高級中學</t>
+          <t>臺南市政府水利局</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>115年製圖桌椅組</t>
+          <t>114年臺南市永華行政區雨水箱涵調查及圖資補正作業(開口合約)(第1次後續擴充)</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>510000</v>
+        <v>8000000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjIzNTU</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191343.xml</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -4870,10 +4870,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -4909,40 +4909,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.87.32</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>臺中市政府消防局</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>115年度海岸地形測量調查分析一式</t>
+          <t>成人全身QCPR心肺復甦訓練模型</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>750000</v>
+        <v>1800000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4982,52 +4982,52 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.13.50</t>
+          <t>3.92.1.27</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>國立北港高級中學</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
+          <t>115年製圖桌椅組</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>17115000</v>
+        <v>510000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjIzNTU</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -5084,35 +5084,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.79.11</t>
+          <t>3.13.50</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
+          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>9166935</v>
+        <v>17115000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5169,35 +5169,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3.97.11</t>
+          <t>3.79.11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>115年度高雄市區域航拍及3D影像建模案</t>
+          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>6000000</v>
+        <v>9166935</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.97.11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5274,15 +5274,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>深海海域地形測量工作一式</t>
+          <t>115年度高雄市區域航拍及3D影像建模案</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1200000</v>
+        <v>6000000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5325,31 +5325,31 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A.13.6.15</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>經濟部水利署第五河川分署</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5359,15 +5359,15 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>115、116年工程設計及用地作業委外測量計畫(開口合約)</t>
+          <t>深海海域地形測量工作一式</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk3NTM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5413,46 +5413,46 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.76.44</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>115年新竹縣智慧圖資雲(功能擴充)案</t>
+          <t>115年度海岸地形測量調查分析一式</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3585000</v>
+        <v>750000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk4MjI</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -5462,19 +5462,19 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5498,56 +5498,56 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A.19</t>
+          <t>A.13.6.15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>經濟部水利署第五河川分署</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>「115年度農地永續利用空間資訊計畫」採購案</t>
+          <t>115、116年工程設計及用地作業委外測量計畫(開口合約)</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>6028000</v>
+        <v>1500000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExMTQ1NDA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk3NTM</t>
         </is>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -5589,40 +5589,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3.87.69</t>
+          <t>3.76.44</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>臺中市大肚區公所</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>115年度臺中市大肚區內道路及排水等維護改善工程(開口契約)委託測量規劃設計監造服務</t>
+          <t>115年新竹縣智慧圖資雲(功能擴充)案</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>225000</v>
+        <v>3585000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA2NDM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk4MjI</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -5632,13 +5632,13 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -5674,40 +5674,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.87.69</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>內政部建築研究所</t>
+          <t>臺中市大肚區公所</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
+          <t>115年度臺中市大肚區內道路及排水等維護改善工程(開口契約)委託測量規劃設計監造服務</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6000000</v>
+        <v>225000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA2NDM</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -5759,35 +5759,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260522</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>20260525</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A.19</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>農業部</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BSA&amp;OFAC模型驗證(三年期)</t>
+          <t>「115年度農地永續利用空間資訊計畫」採購案</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>6028000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260302&amp;fn=PPW-1-70094412.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExMTQ1NDA</t>
         </is>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5820,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -5835,37 +5847,25 @@
           <t>20260522</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>A.19.4.8</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>農業部林業及自然保育署宜蘭分署</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>宜蘭縣</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>115年度宜蘭轄區國有林地占用清理(含勘查、測量及臨時拆除)作業採購案</t>
+          <t>BSA&amp;OFAC模型驗證(三年期)</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>499986</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzNTM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260302&amp;fn=PPW-1-70094412.xml</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -5875,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -5922,35 +5922,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A.41</t>
+          <t>A.19.4.8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>國家發展委員會</t>
+          <t>農業部林業及自然保育署宜蘭分署</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
+          <t>115年度宜蘭轄區國有林地占用清理(含勘查、測量及臨時拆除)作業採購案</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2500000</v>
+        <v>499986</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzNTM</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -6007,35 +6007,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>66557767</t>
+          <t>A.41</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>有限責任國立嘉義高級工業職業學校員生消費合作社</t>
+          <t>國家發展委員會</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>115學年度建築、室設、製圖、機械等科工具採購</t>
+          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>580600</v>
+        <v>2500000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTYwNjA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -6087,22 +6087,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.5.48</t>
+          <t>66557767</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>有限責任國立嘉義高級工業職業學校員生消費合作社</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6112,15 +6112,15 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>訓練用模型槍採購案</t>
+          <t>115學年度建築、室設、製圖、機械等科工具採購</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>4194300</v>
+        <v>580600</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODU4MTA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTYwNjA</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -6172,22 +6172,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3.79.11.7</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>臺北市政府工務局水利工程處</t>
+          <t>內政部建築研究所</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6197,15 +6197,15 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>臺北市河濱自行車道環景圖資建置暨資料介接工作</t>
+          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>950000</v>
+        <v>6000000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQzOTY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -6257,40 +6257,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A.13.6.4</t>
+          <t>3.5.48</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>經濟部水利署水利規劃分署</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>115年淹水數值模型第三次更新輔助管理</t>
+          <t>訓練用模型槍採購案</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>9900000</v>
+        <v>4194300</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNTQyMDY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODU4MTA</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -6347,35 +6347,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A.25.1</t>
+          <t>3.79.11.7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>文化部文化資產局</t>
+          <t>臺北市政府工務局水利工程處</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>「115年文化資產保存修復標準建置計畫-文物3D掃描建模及材質檢測作業指引暨實作驗證」勞務採購案</t>
+          <t>臺北市河濱自行車道環景圖資建置暨資料介接工作</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>4670000</v>
+        <v>950000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODkzNjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQzOTY</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
@@ -6432,35 +6432,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A.19</t>
+          <t>A.13.6.4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>經濟部水利署水利規劃分署</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>115年「犬蹤地圖APP功能擴充及維運計畫」採購案</t>
+          <t>115年淹水數值模型第三次更新輔助管理</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3000000</v>
+        <v>9900000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQyODQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNTQyMDY</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -6517,35 +6517,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A.25</t>
+          <t>A.25.1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>文化部文化資產局</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>115年度文化地圖平台之文化基地徵選活動網站優化案</t>
+          <t>「115年文化資產保存修復標準建置計畫-文物3D掃描建模及材質檢測作業指引暨實作驗證」勞務採購案</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2240000</v>
+        <v>4670000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260520&amp;fn=BDM-1-71182764.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODkzNjU</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
@@ -6597,44 +6597,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A.9.54.3</t>
+          <t>A.19</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>國立成功大學附屬臺南工業高級中等學校</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>土木科測繪用無人機採購案</t>
+          <t>115年「犬蹤地圖APP功能擴充及維運計畫」採購案</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>880000</v>
+        <v>3000000</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTE2NjQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQyODQ</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -6682,85 +6682,340 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A.25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>新北市</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>115年度文化地圖平台之文化基地徵選活動網站優化案</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260520&amp;fn=BDM-1-71182764.xml</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A.9.54.3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>國立成功大學附屬臺南工業高級中等學校</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>南部</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>土木科測繪用無人機採購案</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>880000</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTE2NjQ</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A.19.4.3</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>農業部林業及自然保育署南投分署</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>南投縣</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>115年度測量儀器採購</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1740000</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI5NTU</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>20260518</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>A.13.8.3</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>經濟部產業園區管理局臺南分局</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>臺南市</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>南部</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>台南產業園區等15園區公共設施調查評估及圖資建置</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="G78" t="n">
         <v>2000000</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExMjE4NTk</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6775,7 +7030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6903,17 +7158,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>43862061</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>長庚醫療財團法人林口長庚紀念醫院</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6923,15 +7178,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>115年地政業務地理資訊應用系統增修維護案</t>
+          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2200000</v>
+        <v>2390000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6941,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -6959,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -6988,17 +7243,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>43862061</t>
+          <t>3.79.14.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>長庚醫療財團法人林口長庚紀念醫院</t>
+          <t>臺北市立聯合醫院</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7008,15 +7263,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
+          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2390000</v>
+        <v>686000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -7068,22 +7323,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.80.16.24</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>桃園市楊梅地政事務所</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7093,15 +7348,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115年度圖根點清理與新補建測量作業</t>
+          <t>115年地政業務地理資訊應用系統增修維護案</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>720000</v>
+        <v>2200000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjk4MTI</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -7111,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -7129,7 +7384,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -7153,17 +7408,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A.17.2.2</t>
+          <t>3.80.16.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>桃園市楊梅地政事務所</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7178,15 +7433,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>115年微電腦測量儀（水量測試儀）及專用電腦1批採購案</t>
+          <t>115年度圖根點清理與新補建測量作業</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>676000</v>
+        <v>720000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjY1ODY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjk4MTI</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -7243,17 +7498,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>A.17.2.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7263,15 +7518,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115年度數值地形模型系統維運與加值應用推廣案</t>
+          <t>115年微電腦測量儀（水量測試儀）及專用電腦1批採購案</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1300000</v>
+        <v>676000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk1Nzc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjY1ODY</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -7281,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -7293,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -7311,34 +7566,34 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.76.44</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7348,15 +7603,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
+          <t>115年度數值地形模型系統維運與加值應用推廣案</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7125000</v>
+        <v>1300000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk1Nzc</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -7372,13 +7627,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -7396,13 +7651,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7413,17 +7668,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.10.99.62</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>景文科技大學</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7433,15 +7688,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>115圖資處獎補助中文圖書採購案</t>
+          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>300000</v>
+        <v>31000000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -7498,17 +7753,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.76.44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7518,15 +7773,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
+          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>31000000</v>
+        <v>7125000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -7578,22 +7833,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A.19.6</t>
+          <t>3.10.99.62</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>景文科技大學</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7603,15 +7858,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115-116年度無人飛行載具正射影像產製暨渠道圖資調查研析更新計畫</t>
+          <t>115圖資處獎補助中文圖書採購案</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5280000</v>
+        <v>300000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTczMzE</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -7663,22 +7918,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.80.11</t>
+          <t>A.19.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7688,15 +7943,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>115年度桃園市工廠地理資訊暨稽查管理系統維護計畫</t>
+          <t>115-116年度無人飛行載具正射影像產製暨渠道圖資調查研析更新計畫</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1420000</v>
+        <v>5280000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTUxOTk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTczMzE</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -7712,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -7724,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -7748,22 +8003,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A.7.31.1</t>
+          <t>3.80.11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>臺灣銀行股份有限公司</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7773,15 +8028,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
+          <t>115年度桃園市工廠地理資訊暨稽查管理系統維護計畫</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1995000</v>
+        <v>1420000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTUxOTk</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -7809,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -7821,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -7833,17 +8088,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.79.67.1</t>
+          <t>A.7.31.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>臺北市市場處</t>
+          <t>臺灣銀行股份有限公司</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7858,15 +8113,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
+          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>209000</v>
+        <v>1995000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -7894,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7906,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -7923,12 +8178,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>99334269</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>法務部</t>
+          <t>台灣休閒農業學會</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7943,15 +8198,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
+          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -7970,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7991,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -8008,12 +8263,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99334269</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>台灣休閒農業學會</t>
+          <t>法務部</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8028,15 +8283,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
+          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -8055,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8076,7 +8331,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -8088,17 +8343,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.79.11</t>
+          <t>3.79.67.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>臺北市市場處</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8113,15 +8368,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>115年度管線圖資更新品質案件抽查及抽測作業</t>
+          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7745000</v>
+        <v>209000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODYwNzM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -8137,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -8149,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -8263,12 +8518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>中央研究院</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8283,25 +8538,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
+          <t>光鑷與直接式力測量系統</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3080000</v>
+        <v>6900000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191365.xml</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -8348,12 +8603,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.79.11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中央研究院</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8368,15 +8623,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>光鑷與直接式力測量系統</t>
+          <t>115年度管線圖資更新品質案件抽查及抽測作業</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6900000</v>
+        <v>7745000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191365.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODYwNzM</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -8386,13 +8641,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -8428,17 +8683,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3.79.11</t>
+          <t>3.13.20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8453,15 +8708,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
+          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9166935</v>
+        <v>5100000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -8513,22 +8768,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.76.44</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8538,19 +8793,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>115年新竹縣智慧圖資雲(功能擴充)案</t>
+          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3585000</v>
+        <v>3080000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk4MjI</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -8562,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -8598,17 +8853,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A.19</t>
+          <t>3.79.11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8623,22 +8878,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>「115年度農地永續利用空間資訊計畫」採購案</t>
+          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>6028000</v>
+        <v>9166935</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExMTQ1NDA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -8671,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -8683,22 +8938,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.76.44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>內政部建築研究所</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8708,15 +8963,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
+          <t>115年新竹縣智慧圖資雲(功能擴充)案</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6000000</v>
+        <v>3585000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTk4MjI</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -8732,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -8768,17 +9023,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A.41</t>
+          <t>A.19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>國家發展委員會</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8793,22 +9048,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
+          <t>「115年度農地永續利用空間資訊計畫」採購案</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2500000</v>
+        <v>6028000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExMTQ1NDA</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -8841,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -8853,17 +9108,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.79.11.7</t>
+          <t>A.41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>臺北市政府工務局水利工程處</t>
+          <t>國家發展委員會</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8878,15 +9133,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>臺北市河濱自行車道環景圖資建置暨資料介接工作</t>
+          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>950000</v>
+        <v>2500000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQzOTY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -8902,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -8926,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -8938,22 +9193,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A.19</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>內政部建築研究所</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8963,15 +9218,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>115年「犬蹤地圖APP功能擴充及維運計畫」採購案</t>
+          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQyODQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -9028,80 +9283,250 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>3.79.11.7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>臺北市政府工務局水利工程處</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>臺北市河濱自行車道環景圖資建置暨資料介接工作</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTQzOTY</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A.19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>農業部</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>北部</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>115年「犬蹤地圖APP功能擴充及維運計畫」採購案</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQyODQ</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>A.25</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>文化部</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>新北市</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>北部</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>115年度文化地圖平台之文化基地徵選活動網站優化案</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="G29" t="n">
         <v>2240000</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260520&amp;fn=BDM-1-71182764.xml</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9116,7 +9541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9754,12 +10179,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.87.32</t>
+          <t>A.15.3.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>臺中市政府消防局</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9774,15 +10199,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>成人全身QCPR心肺復甦訓練模型</t>
+          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1800000</v>
+        <v>3960601</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -9798,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -9816,19 +10241,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -9839,12 +10264,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A.15.3.2</t>
+          <t>3.87.32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>臺中市政府消防局</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9859,15 +10284,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
+          <t>成人全身QCPR心肺復甦訓練模型</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3960601</v>
+        <v>1800000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -9883,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -9901,19 +10326,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -10253,6 +10678,91 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A.19.4.3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>農業部林業及自然保育署南投分署</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>南投縣</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>115年度測量儀器採購</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1740000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI5NTU</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10735,17 +11245,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A.9.6J</t>
+          <t>3.9.31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>國立屏東大學</t>
+          <t>國立中正大學</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10755,15 +11265,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
+          <t>115年圖資大樓廁所整修工程</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7152000</v>
+        <v>4610954</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -10820,17 +11330,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.9.31</t>
+          <t>A.9.6J</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>國立中正大學</t>
+          <t>國立屏東大學</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10840,15 +11350,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>115年圖資大樓廁所整修工程</t>
+          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4610954</v>
+        <v>7152000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -11415,17 +11925,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.97.5.4</t>
+          <t>A.13.6.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>高雄市立林園高級中學</t>
+          <t>經濟部水利署南區水資源分署</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11435,15 +11945,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>圖資大樓後續擴充室內裝修工程</t>
+          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>13973553</v>
+        <v>1921585</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -11453,13 +11963,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -11500,17 +12010,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A.13.6.3</t>
+          <t>3.97.5.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>經濟部水利署南區水資源分署</t>
+          <t>高雄市立林園高級中學</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -11520,15 +12030,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
+          <t>圖資大樓後續擴充室內裝修工程</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1921585</v>
+        <v>13973553</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -11538,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -11670,12 +12180,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.13.50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11690,15 +12200,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>115年度海岸地形測量調查分析一式</t>
+          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>750000</v>
+        <v>17115000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -11708,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -11720,7 +12230,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -11738,13 +12248,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -11755,12 +12265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.13.50</t>
+          <t>3.97.11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11775,15 +12285,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
+          <t>115年度高雄市區域航拍及3D影像建模案</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17115000</v>
+        <v>6000000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -11823,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
@@ -11840,12 +12350,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.97.11</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11860,15 +12370,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>115年度高雄市區域航拍及3D影像建模案</t>
+          <t>深海海域地形測量工作一式</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6000000</v>
+        <v>1200000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -11878,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -11890,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -11911,10 +12421,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -11945,15 +12455,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>深海海域地形測量工作一式</t>
+          <t>115年度海岸地形測量調查分析一式</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
         </is>
       </c>
       <c r="I20" t="n">

--- a/data/採購網_決標彙整.xlsx
+++ b/data/採購網_決標彙整.xlsx
@@ -627,35 +627,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>43862061</t>
+          <t>A.15.3.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>長庚醫療財團法人林口長庚紀念醫院</t>
+          <t>交通部公路局東區養護工程分局</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
+          <t>台2線桶盤堀橋改建工程委託測量、地質探查、綜合規劃及設計服務工作</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2390000</v>
+        <v>16444921</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjM4OTY</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -712,17 +712,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A.15.3.4</t>
+          <t>3.13.52.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>交通部公路局東區養護工程分局</t>
+          <t>台灣自來水股份有限公司第十區管理處</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -732,15 +732,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>台2線桶盤堀橋改建工程委託測量、地質探查、綜合規劃及設計服務工作</t>
+          <t>本處113年度新裝及修漏圖資實測定位作業</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>16444921</v>
+        <v>1838580</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjM4OTY</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260617&amp;fn=BDM-1-71207686.xml</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -797,35 +797,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.13.52.10</t>
+          <t>3.79.14.14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第十區管理處</t>
+          <t>臺北市立聯合醫院</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本處113年度新裝及修漏圖資實測定位作業</t>
+          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1838580</v>
+        <v>686000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260617&amp;fn=BDM-1-71207686.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -835,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -882,35 +882,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.79.14.14</t>
+          <t>3.95.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臺北市立聯合醫院</t>
+          <t>臺南市政府水利局</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
+          <t>115年臺南市污水下水道地理資訊系統維護及擴充委託資訊服務</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>686000</v>
+        <v>5000000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTc5NjY</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -965,37 +965,25 @@
           <t>20260617</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3.95.25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>臺南市政府水利局</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>臺南市</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>115年臺南市污水下水道地理資訊系統維護及擴充委託資訊服務</t>
+          <t>「5-L醱酵槽數位模型優化及數位影子建置」委託研究計畫案</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTc5NjY</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20251002&amp;fn=PPW-1-70080650.xml</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1023,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1035,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1050,25 +1038,37 @@
           <t>20260617</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>內政部</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>「5-L醱酵槽數位模型優化及數位影子建置」委託研究計畫案</t>
+          <t>115年地政業務地理資訊應用系統增修維護案</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20251002&amp;fn=PPW-1-70080650.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>43862061</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>長庚醫療財團法人林口長庚紀念醫院</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1145,15 +1145,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>115年地政業務地理資訊應用系統增修維護案</t>
+          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2200000</v>
+        <v>2390000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1793,17 +1793,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.9.31</t>
+          <t>A.9.6J</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>國立中正大學</t>
+          <t>國立屏東大學</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1813,15 +1813,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>115年圖資大樓廁所整修工程</t>
+          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4610954</v>
+        <v>7152000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1876,35 +1876,47 @@
           <t>20260610</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A.19.9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>農業部農業試驗所</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>臺中市</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>臺北市政府地政局所屬所隊115年度測量儀器聯合財物採購案</t>
+          <t>農業環境空間資訊整合及資通訊工具應用推廣教育訓練</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4100000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260327&amp;fn=PPW-1-70097357.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTEwMDU</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1949,37 +1961,25 @@
           <t>20260610</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>A.9.6J</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>國立屏東大學</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>屏東縣</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
+          <t>臺北市政府地政局所屬所隊115年度測量儀器聯合財物採購案</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7152000</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260327&amp;fn=PPW-1-70097357.xml</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1989,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2036,42 +2036,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A.19.9</t>
+          <t>3.9.31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>農業部農業試驗所</t>
+          <t>國立中正大學</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>農業環境空間資訊整合及資通訊工具應用推廣教育訓練</t>
+          <t>115年圖資大樓廁所整修工程</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4100000</v>
+        <v>4610954</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTEwMDU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2376,35 +2376,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.10.90.19</t>
+          <t>3.10.99.62</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南臺學校財團法人南臺科技大學</t>
+          <t>景文科技大學</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>平台式切削動力計測量系統乙套</t>
+          <t>115圖資處獎補助中文圖書採購案</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2353063</v>
+        <v>300000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQxODM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2414,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2459,37 +2459,25 @@
           <t>20260608</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>內政部</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>臺北市</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
+          <t>115-116年東部近岸地形監測</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>31000000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260223&amp;fn=PPW-1-70093777.xml</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2505,13 +2493,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2546,35 +2534,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.76.44</t>
+          <t>3.1.100.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>內政部國土測繪中心</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
+          <t>115年度三維建物模型更新及精進採購案</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7125000</v>
+        <v>18000000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwMTM</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2590,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2614,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2631,17 +2619,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3.10.99.62</t>
+          <t>3.76.44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>景文科技大學</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2651,15 +2639,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>115圖資處獎補助中文圖書採購案</t>
+          <t>115年度新竹縣公共設施管線圖資品質提升暨系統維護改版委託服務案</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>300000</v>
+        <v>7125000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDE2NTU</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2714,25 +2702,37 @@
           <t>20260608</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>內政部</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>115-116年東部近岸地形監測</t>
+          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>31000000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260223&amp;fn=PPW-1-70093777.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2748,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2789,35 +2789,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.1.100.1</t>
+          <t>3.10.90.19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>內政部國土測繪中心</t>
+          <t>南臺學校財團法人南臺科技大學</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>115年度三維建物模型更新及精進採購案</t>
+          <t>平台式切削動力計測量系統乙套</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>18000000</v>
+        <v>2353063</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQxODM</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3639,35 +3639,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.97.13.3</t>
+          <t>A.7.31.1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>高雄市政府警察局交通警察大隊</t>
+          <t>臺灣銀行股份有限公司</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>115年度「交通事故處理淨零轉型專案-建置易肇事路⼝街廓圖資」勞務採購限制性招標案</t>
+          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>750000</v>
+        <v>1995000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTU0NjE=</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3724,35 +3724,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A.7.31.1</t>
+          <t>3.97.13.3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>臺灣銀行股份有限公司</t>
+          <t>高雄市政府警察局交通警察大隊</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>信用卡評分模型監控報表系統資料來源介接調整暨1年維護</t>
+          <t>115年度「交通事故處理淨零轉型專案-建置易肇事路⼝街廓圖資」勞務採購限制性招標案</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1995000</v>
+        <v>750000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260602&amp;fn=BDM-1-71192981.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/urlSelector/common/atm?pk=NzExOTU0NjE=</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>99334269</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>台灣休閒農業學會</t>
+          <t>法務部</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3829,15 +3829,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
+          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3894,35 +3894,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A.13.6.3</t>
+          <t>3.79.67.1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>經濟部水利署南區水資源分署</t>
+          <t>臺北市市場處</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
+          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1921585</v>
+        <v>209000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3979,35 +3979,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.97.5.4</t>
+          <t>99334269</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高雄市立林園高級中學</t>
+          <t>台灣休閒農業學會</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>圖資大樓後續擴充室內裝修工程</t>
+          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>13973553</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4064,35 +4064,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.97.5.4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>法務部</t>
+          <t>高雄市立林園高級中學</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
+          <t>圖資大樓後續擴充室內裝修工程</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>18000000</v>
+        <v>13973553</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4149,35 +4149,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.79.67.1</t>
+          <t>A.13.6.3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>臺北市市場處</t>
+          <t>經濟部水利署南區水資源分署</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
+          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>209000</v>
+        <v>1921585</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4489,35 +4489,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.13.20</t>
+          <t>A.15.6.10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>經濟部水利署</t>
+          <t>交通部民用航空局馬祖航空站</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>連江縣</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>離島</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
+          <t>南竿機場新建模鑄型高壓變壓器故障委託鑑定案</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5100000</v>
+        <v>1228000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzMTM</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -4557,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
@@ -4574,39 +4574,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A.15.6.10</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>交通部民用航空局馬祖航空站</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>連江縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>離島</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>南竿機場新建模鑄型高壓變壓器故障委託鑑定案</t>
+          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1228000</v>
+        <v>3080000</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>1</v>
@@ -4659,39 +4659,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>A.15.3.2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
+          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3080000</v>
+        <v>3960601</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4733,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -4744,35 +4744,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A.15.3.2</t>
+          <t>3.95.25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>臺南市政府水利局</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>信義工務段優先關注邊坡光達應用暨進階檢測圖資建置計畫(第八期)</t>
+          <t>114年臺南市永華行政區雨水箱涵調查及圖資補正作業(開口合約)(第1次後續擴充)</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3960601</v>
+        <v>8000000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNzQ5MTM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191343.xml</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4829,35 +4829,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3.95.25</t>
+          <t>3.87.32</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>臺南市政府水利局</t>
+          <t>臺中市政府消防局</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>中部</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>114年臺南市永華行政區雨水箱涵調查及圖資補正作業(開口合約)(第1次後續擴充)</t>
+          <t>成人全身QCPR心肺復甦訓練模型</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>8000000</v>
+        <v>1800000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260529&amp;fn=BDM-1-71191343.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -4897,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -4914,35 +4914,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.87.32</t>
+          <t>3.13.20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>臺中市政府消防局</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>成人全身QCPR心肺復甦訓練模型</t>
+          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1800000</v>
+        <v>5100000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQxMzU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.13.50</t>
+          <t>3.97.11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5104,15 +5104,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
+          <t>115年度高雄市區域航拍及3D影像建模案</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>17115000</v>
+        <v>6000000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5152,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
@@ -5169,35 +5169,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3.79.11</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
+          <t>115年度海岸地形測量調查分析一式</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>9166935</v>
+        <v>750000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -5237,13 +5237,13 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.97.11</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5274,15 +5274,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>115年度高雄市區域航拍及3D影像建模案</t>
+          <t>深海海域地形測量工作一式</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6000000</v>
+        <v>1200000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5325,10 +5325,10 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5339,35 +5339,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.79.11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>深海海域地形測量工作一式</t>
+          <t>臺北市政府地政局所屬地政事務所115年度臺北市既有成屋三維地籍產權模型回溯建置聯合勞務採購案</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1200000</v>
+        <v>9166935</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188908.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODQ4NjU</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5407,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.13.50</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5444,15 +5444,15 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>115年度海岸地形測量調查分析一式</t>
+          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>750000</v>
+        <v>17115000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5847,25 +5847,37 @@
           <t>20260522</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A.41</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>國家發展委員會</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>北部</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BSA&amp;OFAC模型驗證(三年期)</t>
+          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260302&amp;fn=PPW-1-70094412.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -5922,35 +5934,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A.19.4.8</t>
+          <t>66557767</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署宜蘭分署</t>
+          <t>有限責任國立嘉義高級工業職業學校員生消費合作社</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>東部</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>115年度宜蘭轄區國有林地占用清理(含勘查、測量及臨時拆除)作業採購案</t>
+          <t>115學年度建築、室設、製圖、機械等科工具採購</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>499986</v>
+        <v>580600</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzNTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTYwNjA</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5960,10 +5972,10 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -6007,17 +6019,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A.41</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>國家發展委員會</t>
+          <t>內政部建築研究所</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6027,15 +6039,15 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>「臺灣經濟季預測與多模型整合應用」委託辦理計畫案</t>
+          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2500000</v>
+        <v>6000000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6054,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -6075,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -6092,35 +6104,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>66557767</t>
+          <t>A.19.4.8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>有限責任國立嘉義高級工業職業學校員生消費合作社</t>
+          <t>農業部林業及自然保育署宜蘭分署</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>東部</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>115學年度建築、室設、製圖、機械等科工具採購</t>
+          <t>115年度宜蘭轄區國有林地占用清理(含勘查、測量及臨時拆除)作業採購案</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>580600</v>
+        <v>499986</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTYwNjA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDMzNTM</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -6130,10 +6142,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -6175,37 +6187,25 @@
           <t>20260522</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>3.1.7</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>內政部建築研究所</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>新北市</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>北部</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>「台灣都市通風地圖系統應用與驗證分析(三)」業務委託之專業服務案</t>
+          <t>BSA&amp;OFAC模型驗證(三年期)</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExNjAwNzc</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260302&amp;fn=PPW-1-70094412.xml</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43862061</t>
+          <t>3.79.14.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>長庚醫療財團法人林口長庚紀念醫院</t>
+          <t>臺北市立聯合醫院</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7178,15 +7178,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
+          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2390000</v>
+        <v>686000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.79.14.14</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>臺北市立聯合醫院</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7263,15 +7263,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>電子磅秤(坐式、輪椅式)、扶手秤含身高測量</t>
+          <t>115年地政業務地理資訊應用系統增修維護案</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>686000</v>
+        <v>2200000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjU4MTA</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -7281,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -7328,17 +7328,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>43862061</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>長庚醫療財團法人林口長庚紀念醫院</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7348,15 +7348,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115年地政業務地理資訊應用系統增修維護案</t>
+          <t>VYNTUS CPX運動心肺功能測量儀 規格詳如材料規範 共1ST</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2200000</v>
+        <v>2390000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM1NjU</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTI4MjM</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -7366,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -7668,17 +7668,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10.99.62</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>景文科技大學</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7688,15 +7688,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
+          <t>115圖資處獎補助中文圖書採購案</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>31000000</v>
+        <v>300000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -7838,17 +7838,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.10.99.62</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>景文科技大學</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7858,15 +7858,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>115圖資處獎補助中文圖書採購案</t>
+          <t>115至116年度導航定位模組系統整合與數位道路圖資應用工作案</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>300000</v>
+        <v>31000000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMjQxMTM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExODc4NDc</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>99334269</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台灣休閒農業學會</t>
+          <t>法務部</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8198,15 +8198,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
+          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8246,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.79.67.1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>法務部</t>
+          <t>臺北市市場處</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8283,15 +8283,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>法務部115年度「法務專屬語言模型推論服務系統及其相關功能」開發案</t>
+          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>18000000</v>
+        <v>209000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDQyNjk</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8331,7 +8331,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.79.67.1</t>
+          <t>99334269</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>臺北市市場處</t>
+          <t>台灣休閒農業學會</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8368,15 +8368,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>114年度攤販地理資訊系統維護案-第2次契約變更</t>
+          <t>115年度休閒農場友善環境指引地圖輔導試辦計畫委託專業服務案</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>209000</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260601&amp;fn=BDM-1-71192884.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTM5NDk</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -8395,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3.13.20</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>經濟部水利署</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8708,19 +8708,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
+          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5100000</v>
+        <v>3080000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.13.20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8793,19 +8793,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>115-116年度測繪資訊成果供應管理系統維護工作案</t>
+          <t>水庫水質優養化與碳排預測之智慧模型發展-以南部水庫為例</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3080000</v>
+        <v>5100000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTkwODg</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDUwNzI</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -11245,17 +11245,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.9.31</t>
+          <t>A.9.6J</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>國立中正大學</t>
+          <t>國立屏東大學</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -11265,15 +11265,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115年圖資大樓廁所整修工程</t>
+          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4610954</v>
+        <v>7152000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -11330,17 +11330,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A.9.6J</t>
+          <t>3.9.31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>國立屏東大學</t>
+          <t>國立中正大學</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11350,15 +11350,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>屏商校區圖資大樓12樓教學空間室內裝修工程</t>
+          <t>115年圖資大樓廁所整修工程</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7152000</v>
+        <v>4610954</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTUxNzM</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTk4NTQ</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -11925,17 +11925,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A.13.6.3</t>
+          <t>3.97.5.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>經濟部水利署南區水資源分署</t>
+          <t>高雄市立林園高級中學</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11945,15 +11945,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
+          <t>圖資大樓後續擴充室內裝修工程</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1921585</v>
+        <v>13973553</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -11963,13 +11963,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -12010,17 +12010,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.97.5.4</t>
+          <t>A.13.6.3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>高雄市立林園高級中學</t>
+          <t>經濟部水利署南區水資源分署</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -12030,15 +12030,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>圖資大樓後續擴充室內裝修工程</t>
+          <t>115年度甲仙攔河堰引水隧道3D影像掃描測量工作</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>13973553</v>
+        <v>1921585</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzExOTA4NjY</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMTA0OTQ</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -12048,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -12180,12 +12180,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.13.50</t>
+          <t>3.97.11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12200,15 +12200,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
+          <t>115年度高雄市區域航拍及3D影像建模案</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>17115000</v>
+        <v>6000000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -12248,10 +12248,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
@@ -12265,12 +12265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.97.11</t>
+          <t>3.9.28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>國立中山大學</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12285,15 +12285,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>115年度高雄市區域航拍及3D影像建模案</t>
+          <t>115年度海岸地形測量調查分析一式</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6000000</v>
+        <v>750000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188530.xml</t>
+          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -12303,7 +12303,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -12336,10 +12336,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3.9.28</t>
+          <t>3.13.50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>國立中山大學</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12455,15 +12455,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>115年度海岸地形測量調查分析一式</t>
+          <t>Siemens gPROMS輕油裂解爐數位雙生製程模型建立服務</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>750000</v>
+        <v>17115000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://web.pcc.gov.tw/prkms/tender/common/noticeDate/redirectPublic?ds=20260527&amp;fn=BDM-1-71188893.xml</t>
+          <t>https://web.pcc.gov.tw/tps/QueryTender/query/searchTenderDetail?pkPmsMain=NzEyMDY4NjM</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -12473,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -12485,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -12503,13 +12503,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
